--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>13439.56</v>
+        <v>13359.01</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>39665.57</v>
+        <v>39427.84</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9825.18</v>
+        <v>9691.6</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7472.85</v>
+        <v>7409.11</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8873.24</v>
+        <v>8921.02</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>16473.36</v>
+        <v>16562.07</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7056.31</v>
+        <v>7135.23</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11381.53</v>
+        <v>11508.82</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9854.379999999999</v>
+        <v>9964.59</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>29430.3</v>
+        <v>29653.22</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5629.72</v>
+        <v>5672.37</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>11664.78</v>
+        <v>11753.14</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>14656.88</v>
+        <v>14712.41</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6523.45</v>
+        <v>6548.16</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23066.26</v>
+        <v>23008.02</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12310.94</v>
+        <v>12279.86</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>16310.24</v>
+        <v>16269.06</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>13485.71</v>
+        <v>13451.66</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9262.639999999999</v>
+        <v>9239.26</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7319.35</v>
+        <v>7300.87</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13919.87</v>
+        <v>13884.72</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7498.34</v>
+        <v>7569.58</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7457.34</v>
+        <v>7528.19</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10365.67</v>
+        <v>10464.15</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9466.639999999999</v>
+        <v>9556.58</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>14770.58</v>
+        <v>14910.91</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>9852.889999999999</v>
+        <v>9926.299999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>18887.13</v>
+        <v>19027.83</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>18437.69</v>
+        <v>18575.05</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>41730.15</v>
+        <v>41313.99</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>19379.94</v>
+        <v>19186.66</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>9520.1</v>
+        <v>9478.370000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>11700.33</v>
+        <v>11649.04</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>14954.25</v>
+        <v>14888.7</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>9180.18</v>
+        <v>9080.32</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>8021.18</v>
+        <v>7933.92</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>28750.92</v>
+        <v>28685.66</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>18676.77</v>
+        <v>18630.65</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>28406.58</v>
+        <v>28336.43</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>37877.19</v>
+        <v>37783.66</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>12544.31</v>
+        <v>12513.33</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11227.9</v>
+        <v>11283.05</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7570.42</v>
+        <v>7607.61</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12111.37</v>
+        <v>12170.86</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7096.43</v>
+        <v>7131.29</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>106544.88</v>
+        <v>106898.33</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>16703.89</v>
+        <v>16759.3</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>10316.53</v>
+        <v>10350.76</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>12338.38</v>
+        <v>12377.65</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>13001.7</v>
+        <v>13043.08</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>17109.45</v>
+        <v>17163.91</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13975.49</v>
+        <v>14019.97</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>46477.6</v>
+        <v>46625.52</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>27266.56</v>
+        <v>27411.55</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>31613.93</v>
+        <v>31782.04</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>13412.32</v>
+        <v>13483.64</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2098,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2289,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2354,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2541,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2606,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2732,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2919,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2984,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3049,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3114,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3362,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3549,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3679,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3805,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3931,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +3996,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4061,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/may-2026.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
